--- a/diseases/d051/2010-2014.xlsx
+++ b/diseases/d051/2010-2014.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -922,6 +927,11 @@
       <c r="S3" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">

--- a/diseases/d051/2010-2014.xlsx
+++ b/diseases/d051/2010-2014.xlsx
@@ -776,33 +776,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>HOLD_CH_d1b564fb561c1baf80f34e9e37f9</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>HOLD_CH_d1b564fb561c1baf80f34e9e37f9</t>
+        </is>
+      </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -929,33 +938,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>HOLD_CH_d1b564fb561c1baf80f34e9e37f9</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>HOLD_CH_d1b564fb561c1baf80f34e9e37f9</t>
+        </is>
+      </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">

--- a/diseases/d051/2010-2014.xlsx
+++ b/diseases/d051/2010-2014.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>HOLD_CH_d1b564fb561c1baf80f34e9e37f9</t>
@@ -793,12 +788,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -809,11 +799,6 @@
       <c r="AT2" t="n">
         <v>1</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -933,11 +918,6 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>HOLD_CH_d1b564fb561c1baf80f34e9e37f9</t>
@@ -955,12 +935,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -970,11 +945,6 @@
       </c>
       <c r="AT3" t="n">
         <v>1</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>

--- a/diseases/d051/2010-2014.xlsx
+++ b/diseases/d051/2010-2014.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>HOLD_CH_d1b564fb561c1baf80f34e9e37f9</t>
@@ -788,7 +793,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -799,6 +809,11 @@
       <c r="AT2" t="n">
         <v>1</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -918,6 +933,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>HOLD_CH_d1b564fb561c1baf80f34e9e37f9</t>
@@ -935,7 +955,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -945,6 +970,11 @@
       </c>
       <c r="AT3" t="n">
         <v>1</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
